--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N70_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9685873180377113</v>
+        <v>0.1573954391811281</v>
       </c>
       <c r="D2" t="n">
-        <v>1.603342492796249</v>
+        <v>0.2605431550793904</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
